--- a/구매 업무 자동화/BOM/BOM.xlsx
+++ b/구매 업무 자동화/BOM/BOM.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seunghyunwoo\Desktop\github\SCMAUTO\구매 업무 자동화\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD51FDAE-4C36-48F8-A040-2D188C4BA487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E02A93-47A6-4F1A-8484-BCF4253E9004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4695" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{652A96A7-B3A7-4977-8216-1E6948D08560}"/>
+    <workbookView xWindow="38280" yWindow="3780" windowWidth="29040" windowHeight="15720" xr2:uid="{652A96A7-B3A7-4977-8216-1E6948D08560}"/>
   </bookViews>
   <sheets>
     <sheet name="파싱용" sheetId="3" r:id="rId1"/>
-    <sheet name="BOM_(신조) HiNAS Nav" sheetId="4" state="hidden" r:id="rId2"/>
-    <sheet name="BOM_(신조) HiNAS Nav DOM" sheetId="5" state="hidden" r:id="rId3"/>
-    <sheet name="BOM_(신조) HiNAS Control" sheetId="6" state="hidden" r:id="rId4"/>
-    <sheet name="BOM_(신조) HiNAS Con V2" sheetId="7" state="hidden" r:id="rId5"/>
-    <sheet name="BOM_(신조) HiNAS SVM" sheetId="8" state="hidden" r:id="rId6"/>
-    <sheet name="BOM_(개조) HiNAS Con SVM" sheetId="9" state="hidden" r:id="rId7"/>
-    <sheet name="BOM_(개조) HiNAS Control" sheetId="10" state="hidden" r:id="rId8"/>
-    <sheet name="자재리스트" sheetId="11" state="hidden" r:id="rId9"/>
-    <sheet name="완제품리스트" sheetId="12" state="hidden" r:id="rId10"/>
+    <sheet name="BOM_(신조) HiNAS Nav" sheetId="4" r:id="rId2"/>
+    <sheet name="BOM_(신조) HiNAS Nav DOM" sheetId="5" r:id="rId3"/>
+    <sheet name="BOM_(신조) HiNAS Control" sheetId="6" r:id="rId4"/>
+    <sheet name="BOM_(신조) HiNAS Con V2" sheetId="7" r:id="rId5"/>
+    <sheet name="BOM_(신조) HiNAS SVM" sheetId="8" r:id="rId6"/>
+    <sheet name="BOM_(개조) HiNAS Con SVM" sheetId="9" r:id="rId7"/>
+    <sheet name="BOM_(개조) HiNAS Control" sheetId="10" r:id="rId8"/>
+    <sheet name="자재리스트" sheetId="11" r:id="rId9"/>
+    <sheet name="완제품리스트" sheetId="12" r:id="rId10"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId11"/>
   </sheets>
   <externalReferences>
@@ -3706,16 +3706,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3724,10 +3727,19 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -3761,18 +3773,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5604,10 +5604,10 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="109" t="s">
         <v>561</v>
       </c>
       <c r="C2" s="3" t="str">
@@ -5646,14 +5646,14 @@
       <c r="N2" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="P2" s="109" t="s">
+      <c r="P2" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="110"/>
+      <c r="Q2" s="111"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A3" s="107"/>
-      <c r="B3" s="107"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="109"/>
       <c r="C3" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B12</f>
         <v>SS0001</v>
@@ -5678,7 +5678,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O12</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K3" s="111" t="s">
+      <c r="K3" s="113" t="s">
         <v>12</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -5698,8 +5698,8 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="107"/>
-      <c r="B4" s="107"/>
+      <c r="A4" s="109"/>
+      <c r="B4" s="109"/>
       <c r="C4" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B13</f>
         <v>SZ0013</v>
@@ -5724,7 +5724,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O13</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K4" s="112"/>
+      <c r="K4" s="114"/>
       <c r="L4" s="8" t="s">
         <v>16</v>
       </c>
@@ -5742,8 +5742,8 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="107"/>
-      <c r="B5" s="107"/>
+      <c r="A5" s="109"/>
+      <c r="B5" s="109"/>
       <c r="C5" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B14</f>
         <v>SC0004</v>
@@ -5768,7 +5768,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O14</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K5" s="112"/>
+      <c r="K5" s="114"/>
       <c r="L5" s="8" t="s">
         <v>18</v>
       </c>
@@ -5786,8 +5786,8 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="107"/>
-      <c r="B6" s="107"/>
+      <c r="A6" s="109"/>
+      <c r="B6" s="109"/>
       <c r="C6" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B15</f>
         <v>SC0010</v>
@@ -5812,7 +5812,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O15</f>
         <v>w. GMSL cable</v>
       </c>
-      <c r="K6" s="112"/>
+      <c r="K6" s="114"/>
       <c r="L6" s="8" t="s">
         <v>21</v>
       </c>
@@ -5830,8 +5830,8 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A7" s="107"/>
-      <c r="B7" s="107"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="109"/>
       <c r="C7" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B16</f>
         <v>SC0002</v>
@@ -5856,7 +5856,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O16</f>
         <v>w. VPC KIT</v>
       </c>
-      <c r="K7" s="112"/>
+      <c r="K7" s="114"/>
       <c r="L7" s="8" t="s">
         <v>24</v>
       </c>
@@ -5870,8 +5870,8 @@
       <c r="Q7" s="12"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
+      <c r="A8" s="109"/>
+      <c r="B8" s="109"/>
       <c r="C8" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B17</f>
         <v>SC0003</v>
@@ -5896,7 +5896,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O17</f>
         <v>1세대 용 (직경 42mm)</v>
       </c>
-      <c r="K8" s="112"/>
+      <c r="K8" s="114"/>
       <c r="L8" s="8" t="s">
         <v>25</v>
       </c>
@@ -5910,8 +5910,8 @@
       <c r="Q8" s="12"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A9" s="107"/>
-      <c r="B9" s="107"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="109"/>
       <c r="C9" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B18</f>
         <v>SC0005</v>
@@ -5936,7 +5936,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O18</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K9" s="112"/>
+      <c r="K9" s="114"/>
       <c r="L9" s="8" t="s">
         <v>26</v>
       </c>
@@ -5948,8 +5948,8 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A10" s="107"/>
-      <c r="B10" s="107"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="109"/>
       <c r="C10" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B19</f>
         <v>SS0003</v>
@@ -5974,7 +5974,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O19</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K10" s="112"/>
+      <c r="K10" s="114"/>
       <c r="L10" s="8" t="s">
         <v>28</v>
       </c>
@@ -5986,8 +5986,8 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A11" s="107"/>
-      <c r="B11" s="107"/>
+      <c r="A11" s="109"/>
+      <c r="B11" s="109"/>
       <c r="C11" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B20</f>
         <v>SZ0012</v>
@@ -6012,7 +6012,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O20</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K11" s="112"/>
+      <c r="K11" s="114"/>
       <c r="L11" s="8" t="s">
         <v>31</v>
       </c>
@@ -6024,8 +6024,8 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12" s="107"/>
-      <c r="B12" s="107"/>
+      <c r="A12" s="109"/>
+      <c r="B12" s="109"/>
       <c r="C12" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B21</f>
         <v>SZ0014</v>
@@ -6050,7 +6050,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O21</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K12" s="112"/>
+      <c r="K12" s="114"/>
       <c r="L12" s="8" t="s">
         <v>33</v>
       </c>
@@ -6062,8 +6062,8 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13" s="107"/>
-      <c r="B13" s="107"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="109"/>
       <c r="C13" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B22</f>
         <v>SB0002</v>
@@ -6088,7 +6088,7 @@
         <f>'BOM_(신조) HiNAS Nav'!O22</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K13" s="112"/>
+      <c r="K13" s="114"/>
       <c r="L13" s="7" t="s">
         <v>34</v>
       </c>
@@ -6100,8 +6100,8 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14" s="107"/>
-      <c r="B14" s="107"/>
+      <c r="A14" s="109"/>
+      <c r="B14" s="109"/>
       <c r="C14" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B23</f>
         <v>SE0003</v>
@@ -6126,14 +6126,14 @@
         <f>'BOM_(신조) HiNAS Nav'!O23</f>
         <v>마린필터, network card, 케이블 포함</v>
       </c>
-      <c r="K14" s="126"/>
-      <c r="L14" s="127"/>
-      <c r="M14" s="127"/>
-      <c r="N14" s="127"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15" s="107"/>
-      <c r="B15" s="107"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="109"/>
       <c r="C15" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B24</f>
         <v>SZ0019</v>
@@ -6158,14 +6158,14 @@
         <f>'BOM_(신조) HiNAS Nav'!O24</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="K15" s="124"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="106"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" s="107"/>
-      <c r="B16" s="107"/>
+      <c r="A16" s="109"/>
+      <c r="B16" s="109"/>
       <c r="C16" s="3" t="str">
         <f>'BOM_(신조) HiNAS Nav'!B25</f>
         <v>SZ0020</v>
@@ -6192,10 +6192,10 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="112" t="s">
         <v>560</v>
       </c>
       <c r="C17" s="13" t="str">
@@ -6224,8 +6224,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A18" s="108"/>
-      <c r="B18" s="108"/>
+      <c r="A18" s="112"/>
+      <c r="B18" s="112"/>
       <c r="C18" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B12</f>
         <v>SS0001</v>
@@ -6252,8 +6252,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="108"/>
-      <c r="B19" s="108"/>
+      <c r="A19" s="112"/>
+      <c r="B19" s="112"/>
       <c r="C19" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B13</f>
         <v>SZ0013</v>
@@ -6280,8 +6280,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20" s="108"/>
-      <c r="B20" s="108"/>
+      <c r="A20" s="112"/>
+      <c r="B20" s="112"/>
       <c r="C20" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B14</f>
         <v>SB0004</v>
@@ -6308,8 +6308,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="108"/>
-      <c r="B21" s="108"/>
+      <c r="A21" s="112"/>
+      <c r="B21" s="112"/>
       <c r="C21" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B15</f>
         <v>SB0002</v>
@@ -6336,8 +6336,8 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
       <c r="C22" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B16</f>
         <v>SC0004</v>
@@ -6364,8 +6364,8 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="108"/>
-      <c r="B23" s="108"/>
+      <c r="A23" s="112"/>
+      <c r="B23" s="112"/>
       <c r="C23" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B17</f>
         <v>SC0010</v>
@@ -6392,8 +6392,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="108"/>
-      <c r="B24" s="108"/>
+      <c r="A24" s="112"/>
+      <c r="B24" s="112"/>
       <c r="C24" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B18</f>
         <v>SC0002</v>
@@ -6420,8 +6420,8 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="108"/>
-      <c r="B25" s="108"/>
+      <c r="A25" s="112"/>
+      <c r="B25" s="112"/>
       <c r="C25" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B19</f>
         <v>SC0003</v>
@@ -6448,8 +6448,8 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" s="108"/>
-      <c r="B26" s="108"/>
+      <c r="A26" s="112"/>
+      <c r="B26" s="112"/>
       <c r="C26" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B20</f>
         <v>SC0005</v>
@@ -6476,8 +6476,8 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A27" s="108"/>
-      <c r="B27" s="108"/>
+      <c r="A27" s="112"/>
+      <c r="B27" s="112"/>
       <c r="C27" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B21</f>
         <v>SS0003</v>
@@ -6504,8 +6504,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A28" s="108"/>
-      <c r="B28" s="108"/>
+      <c r="A28" s="112"/>
+      <c r="B28" s="112"/>
       <c r="C28" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B22</f>
         <v>SZ0012</v>
@@ -6532,8 +6532,8 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" s="108"/>
-      <c r="B29" s="108"/>
+      <c r="A29" s="112"/>
+      <c r="B29" s="112"/>
       <c r="C29" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B23</f>
         <v>SZ0014</v>
@@ -6560,8 +6560,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" s="108"/>
-      <c r="B30" s="108"/>
+      <c r="A30" s="112"/>
+      <c r="B30" s="112"/>
       <c r="C30" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B24</f>
         <v>SE0003</v>
@@ -6588,8 +6588,8 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A31" s="108"/>
-      <c r="B31" s="108"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="112"/>
       <c r="C31" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B25</f>
         <v>SZ0019</v>
@@ -6616,8 +6616,8 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A32" s="108"/>
-      <c r="B32" s="108"/>
+      <c r="A32" s="112"/>
+      <c r="B32" s="112"/>
       <c r="C32" s="13" t="str">
         <f>'BOM_(신조) HiNAS Nav DOM'!B26</f>
         <v>SZ0020</v>
@@ -6644,10 +6644,10 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A33" s="107" t="s">
+      <c r="A33" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="109" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3" t="str">
@@ -6676,8 +6676,8 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A34" s="107"/>
-      <c r="B34" s="107"/>
+      <c r="A34" s="109"/>
+      <c r="B34" s="109"/>
       <c r="C34" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B12</f>
         <v>SM0003</v>
@@ -6704,8 +6704,8 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" s="107"/>
-      <c r="B35" s="107"/>
+      <c r="A35" s="109"/>
+      <c r="B35" s="109"/>
       <c r="C35" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B13</f>
         <v>SS0001</v>
@@ -6732,8 +6732,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A36" s="107"/>
-      <c r="B36" s="107"/>
+      <c r="A36" s="109"/>
+      <c r="B36" s="109"/>
       <c r="C36" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B14</f>
         <v>SS0002</v>
@@ -6760,8 +6760,8 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A37" s="107"/>
-      <c r="B37" s="107"/>
+      <c r="A37" s="109"/>
+      <c r="B37" s="109"/>
       <c r="C37" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B15</f>
         <v>SZ0006</v>
@@ -6788,8 +6788,8 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A38" s="107"/>
-      <c r="B38" s="107"/>
+      <c r="A38" s="109"/>
+      <c r="B38" s="109"/>
       <c r="C38" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B16</f>
         <v>SC0004</v>
@@ -6816,8 +6816,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A39" s="107"/>
-      <c r="B39" s="107"/>
+      <c r="A39" s="109"/>
+      <c r="B39" s="109"/>
       <c r="C39" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B17</f>
         <v>SC0010</v>
@@ -6844,8 +6844,8 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A40" s="107"/>
-      <c r="B40" s="107"/>
+      <c r="A40" s="109"/>
+      <c r="B40" s="109"/>
       <c r="C40" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B18</f>
         <v>SC0002</v>
@@ -6872,8 +6872,8 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A41" s="107"/>
-      <c r="B41" s="107"/>
+      <c r="A41" s="109"/>
+      <c r="B41" s="109"/>
       <c r="C41" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B19</f>
         <v>SC0003</v>
@@ -6900,8 +6900,8 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A42" s="107"/>
-      <c r="B42" s="107"/>
+      <c r="A42" s="109"/>
+      <c r="B42" s="109"/>
       <c r="C42" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B20</f>
         <v>SC0005</v>
@@ -6928,8 +6928,8 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" s="107"/>
-      <c r="B43" s="107"/>
+      <c r="A43" s="109"/>
+      <c r="B43" s="109"/>
       <c r="C43" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B21</f>
         <v>SS0003</v>
@@ -6956,8 +6956,8 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A44" s="107"/>
-      <c r="B44" s="107"/>
+      <c r="A44" s="109"/>
+      <c r="B44" s="109"/>
       <c r="C44" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B22</f>
         <v>SZ0012</v>
@@ -6984,8 +6984,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A45" s="107"/>
-      <c r="B45" s="107"/>
+      <c r="A45" s="109"/>
+      <c r="B45" s="109"/>
       <c r="C45" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B23</f>
         <v>SZ0014</v>
@@ -7012,8 +7012,8 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A46" s="107"/>
-      <c r="B46" s="107"/>
+      <c r="A46" s="109"/>
+      <c r="B46" s="109"/>
       <c r="C46" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B24</f>
         <v>SZ0007</v>
@@ -7040,8 +7040,8 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A47" s="107"/>
-      <c r="B47" s="107"/>
+      <c r="A47" s="109"/>
+      <c r="B47" s="109"/>
       <c r="C47" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B25</f>
         <v>SB0002</v>
@@ -7068,8 +7068,8 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A48" s="107"/>
-      <c r="B48" s="107"/>
+      <c r="A48" s="109"/>
+      <c r="B48" s="109"/>
       <c r="C48" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B26</f>
         <v>SB0006</v>
@@ -7096,8 +7096,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" s="107"/>
-      <c r="B49" s="107"/>
+      <c r="A49" s="109"/>
+      <c r="B49" s="109"/>
       <c r="C49" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B27</f>
         <v>SB0013</v>
@@ -7124,8 +7124,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A50" s="107"/>
-      <c r="B50" s="107"/>
+      <c r="A50" s="109"/>
+      <c r="B50" s="109"/>
       <c r="C50" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B28</f>
         <v>SB0004</v>
@@ -7152,8 +7152,8 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A51" s="107"/>
-      <c r="B51" s="107"/>
+      <c r="A51" s="109"/>
+      <c r="B51" s="109"/>
       <c r="C51" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B29</f>
         <v>SB0011</v>
@@ -7180,8 +7180,8 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A52" s="107"/>
-      <c r="B52" s="107"/>
+      <c r="A52" s="109"/>
+      <c r="B52" s="109"/>
       <c r="C52" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B30</f>
         <v>SE0001</v>
@@ -7208,8 +7208,8 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A53" s="107"/>
-      <c r="B53" s="107"/>
+      <c r="A53" s="109"/>
+      <c r="B53" s="109"/>
       <c r="C53" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B31</f>
         <v>SZ0019</v>
@@ -7236,8 +7236,8 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A54" s="107"/>
-      <c r="B54" s="107"/>
+      <c r="A54" s="109"/>
+      <c r="B54" s="109"/>
       <c r="C54" s="3" t="str">
         <f>'BOM_(신조) HiNAS Control'!B32</f>
         <v>SZ0020</v>
@@ -7264,10 +7264,10 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A55" s="108" t="s">
+      <c r="A55" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="108" t="s">
+      <c r="B55" s="112" t="s">
         <v>559</v>
       </c>
       <c r="C55" s="13" t="str">
@@ -7296,8 +7296,8 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" s="108"/>
-      <c r="B56" s="108"/>
+      <c r="A56" s="112"/>
+      <c r="B56" s="112"/>
       <c r="C56" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B12</f>
         <v>SM0003</v>
@@ -7324,8 +7324,8 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A57" s="108"/>
-      <c r="B57" s="108"/>
+      <c r="A57" s="112"/>
+      <c r="B57" s="112"/>
       <c r="C57" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B13</f>
         <v>SS0001</v>
@@ -7352,8 +7352,8 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A58" s="108"/>
-      <c r="B58" s="108"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="112"/>
       <c r="C58" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B14</f>
         <v>SS0002</v>
@@ -7380,8 +7380,8 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A59" s="108"/>
-      <c r="B59" s="108"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="112"/>
       <c r="C59" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B15</f>
         <v>SZ0006</v>
@@ -7408,8 +7408,8 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A60" s="108"/>
-      <c r="B60" s="108"/>
+      <c r="A60" s="112"/>
+      <c r="B60" s="112"/>
       <c r="C60" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B16</f>
         <v>SC0020</v>
@@ -7436,8 +7436,8 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" s="108"/>
-      <c r="B61" s="108"/>
+      <c r="A61" s="112"/>
+      <c r="B61" s="112"/>
       <c r="C61" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B17</f>
         <v>SC0016</v>
@@ -7464,8 +7464,8 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A62" s="108"/>
-      <c r="B62" s="108"/>
+      <c r="A62" s="112"/>
+      <c r="B62" s="112"/>
       <c r="C62" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B18</f>
         <v>SC0018</v>
@@ -7492,8 +7492,8 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A63" s="108"/>
-      <c r="B63" s="108"/>
+      <c r="A63" s="112"/>
+      <c r="B63" s="112"/>
       <c r="C63" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B19</f>
         <v>SC0002</v>
@@ -7520,8 +7520,8 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A64" s="108"/>
-      <c r="B64" s="108"/>
+      <c r="A64" s="112"/>
+      <c r="B64" s="112"/>
       <c r="C64" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B20</f>
         <v>SC0019</v>
@@ -7548,8 +7548,8 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A65" s="108"/>
-      <c r="B65" s="108"/>
+      <c r="A65" s="112"/>
+      <c r="B65" s="112"/>
       <c r="C65" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B21</f>
         <v>SZ0007</v>
@@ -7576,8 +7576,8 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A66" s="108"/>
-      <c r="B66" s="108"/>
+      <c r="A66" s="112"/>
+      <c r="B66" s="112"/>
       <c r="C66" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B22</f>
         <v>SB0002</v>
@@ -7604,8 +7604,8 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A67" s="108"/>
-      <c r="B67" s="108"/>
+      <c r="A67" s="112"/>
+      <c r="B67" s="112"/>
       <c r="C67" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B23</f>
         <v>SB0006</v>
@@ -7632,8 +7632,8 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A68" s="108"/>
-      <c r="B68" s="108"/>
+      <c r="A68" s="112"/>
+      <c r="B68" s="112"/>
       <c r="C68" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B24</f>
         <v>SB0013</v>
@@ -7660,8 +7660,8 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A69" s="108"/>
-      <c r="B69" s="108"/>
+      <c r="A69" s="112"/>
+      <c r="B69" s="112"/>
       <c r="C69" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B25</f>
         <v>SB0004</v>
@@ -7688,8 +7688,8 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A70" s="108"/>
-      <c r="B70" s="108"/>
+      <c r="A70" s="112"/>
+      <c r="B70" s="112"/>
       <c r="C70" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B26</f>
         <v>SB0011</v>
@@ -7716,8 +7716,8 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A71" s="108"/>
-      <c r="B71" s="108"/>
+      <c r="A71" s="112"/>
+      <c r="B71" s="112"/>
       <c r="C71" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B27</f>
         <v>SE0001</v>
@@ -7744,8 +7744,8 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A72" s="108"/>
-      <c r="B72" s="108"/>
+      <c r="A72" s="112"/>
+      <c r="B72" s="112"/>
       <c r="C72" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B28</f>
         <v>SZ0019</v>
@@ -7772,8 +7772,8 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A73" s="108"/>
-      <c r="B73" s="108"/>
+      <c r="A73" s="112"/>
+      <c r="B73" s="112"/>
       <c r="C73" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B29</f>
         <v>SZ0020</v>
@@ -7800,8 +7800,8 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A74" s="108"/>
-      <c r="B74" s="108"/>
+      <c r="A74" s="112"/>
+      <c r="B74" s="112"/>
       <c r="C74" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B30</f>
         <v>SB0022</v>
@@ -7828,8 +7828,8 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A75" s="108"/>
-      <c r="B75" s="108"/>
+      <c r="A75" s="112"/>
+      <c r="B75" s="112"/>
       <c r="C75" s="13" t="str">
         <f>'BOM_(신조) HiNAS Con V2'!B31</f>
         <v>SB0025</v>
@@ -7856,10 +7856,10 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A76" s="107" t="s">
+      <c r="A76" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="B76" s="107" t="s">
+      <c r="B76" s="109" t="s">
         <v>36</v>
       </c>
       <c r="C76" s="3" t="str">
@@ -7888,8 +7888,8 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A77" s="107"/>
-      <c r="B77" s="107"/>
+      <c r="A77" s="109"/>
+      <c r="B77" s="109"/>
       <c r="C77" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B12</f>
         <v>SS0001</v>
@@ -7916,8 +7916,8 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A78" s="107"/>
-      <c r="B78" s="107"/>
+      <c r="A78" s="109"/>
+      <c r="B78" s="109"/>
       <c r="C78" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B13</f>
         <v>SC0006</v>
@@ -7944,8 +7944,8 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A79" s="107"/>
-      <c r="B79" s="107"/>
+      <c r="A79" s="109"/>
+      <c r="B79" s="109"/>
       <c r="C79" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B14</f>
         <v>SB0022</v>
@@ -7972,8 +7972,8 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A80" s="107"/>
-      <c r="B80" s="107"/>
+      <c r="A80" s="109"/>
+      <c r="B80" s="109"/>
       <c r="C80" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B15</f>
         <v>SB0002</v>
@@ -8000,8 +8000,8 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A81" s="107"/>
-      <c r="B81" s="107"/>
+      <c r="A81" s="109"/>
+      <c r="B81" s="109"/>
       <c r="C81" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B16</f>
         <v>SZ0017</v>
@@ -8028,8 +8028,8 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A82" s="107"/>
-      <c r="B82" s="107"/>
+      <c r="A82" s="109"/>
+      <c r="B82" s="109"/>
       <c r="C82" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B17</f>
         <v>SB0021</v>
@@ -8056,8 +8056,8 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A83" s="107"/>
-      <c r="B83" s="107"/>
+      <c r="A83" s="109"/>
+      <c r="B83" s="109"/>
       <c r="C83" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B18</f>
         <v>SB0014</v>
@@ -8084,8 +8084,8 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A84" s="107"/>
-      <c r="B84" s="107"/>
+      <c r="A84" s="109"/>
+      <c r="B84" s="109"/>
       <c r="C84" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B19</f>
         <v>SZ0002</v>
@@ -8112,8 +8112,8 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A85" s="107"/>
-      <c r="B85" s="107"/>
+      <c r="A85" s="109"/>
+      <c r="B85" s="109"/>
       <c r="C85" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B20</f>
         <v>SZ0010</v>
@@ -8140,8 +8140,8 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A86" s="107"/>
-      <c r="B86" s="107"/>
+      <c r="A86" s="109"/>
+      <c r="B86" s="109"/>
       <c r="C86" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B21</f>
         <v>SB0008</v>
@@ -8168,8 +8168,8 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A87" s="107"/>
-      <c r="B87" s="107"/>
+      <c r="A87" s="109"/>
+      <c r="B87" s="109"/>
       <c r="C87" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B22</f>
         <v>SB0015</v>
@@ -8196,8 +8196,8 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A88" s="107"/>
-      <c r="B88" s="107"/>
+      <c r="A88" s="109"/>
+      <c r="B88" s="109"/>
       <c r="C88" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B23</f>
         <v>SZ0021</v>
@@ -8224,8 +8224,8 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A89" s="107"/>
-      <c r="B89" s="107"/>
+      <c r="A89" s="109"/>
+      <c r="B89" s="109"/>
       <c r="C89" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B24</f>
         <v>SE0003</v>
@@ -8252,8 +8252,8 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A90" s="107"/>
-      <c r="B90" s="107"/>
+      <c r="A90" s="109"/>
+      <c r="B90" s="109"/>
       <c r="C90" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B25</f>
         <v>SZ0019</v>
@@ -8280,8 +8280,8 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A91" s="107"/>
-      <c r="B91" s="107"/>
+      <c r="A91" s="109"/>
+      <c r="B91" s="109"/>
       <c r="C91" s="3" t="str">
         <f>'BOM_(신조) HiNAS SVM'!B26</f>
         <v>SZ0020</v>
@@ -8308,10 +8308,10 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A92" s="105" t="s">
+      <c r="A92" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="B92" s="105" t="s">
+      <c r="B92" s="115" t="s">
         <v>562</v>
       </c>
       <c r="C92" s="14" t="str">
@@ -8340,8 +8340,8 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A93" s="105"/>
-      <c r="B93" s="105"/>
+      <c r="A93" s="115"/>
+      <c r="B93" s="115"/>
       <c r="C93" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B12</f>
         <v>SS0001</v>
@@ -8368,8 +8368,8 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A94" s="105"/>
-      <c r="B94" s="105"/>
+      <c r="A94" s="115"/>
+      <c r="B94" s="115"/>
       <c r="C94" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B13</f>
         <v>SC0006</v>
@@ -8396,8 +8396,8 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A95" s="105"/>
-      <c r="B95" s="105"/>
+      <c r="A95" s="115"/>
+      <c r="B95" s="115"/>
       <c r="C95" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B14</f>
         <v>SB0002</v>
@@ -8424,8 +8424,8 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A96" s="105"/>
-      <c r="B96" s="105"/>
+      <c r="A96" s="115"/>
+      <c r="B96" s="115"/>
       <c r="C96" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B15</f>
         <v>SB0007</v>
@@ -8452,8 +8452,8 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A97" s="105"/>
-      <c r="B97" s="105"/>
+      <c r="A97" s="115"/>
+      <c r="B97" s="115"/>
       <c r="C97" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B16</f>
         <v>SB0008</v>
@@ -8480,8 +8480,8 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A98" s="105"/>
-      <c r="B98" s="105"/>
+      <c r="A98" s="115"/>
+      <c r="B98" s="115"/>
       <c r="C98" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B17</f>
         <v>SZ0001</v>
@@ -8508,8 +8508,8 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A99" s="105"/>
-      <c r="B99" s="105"/>
+      <c r="A99" s="115"/>
+      <c r="B99" s="115"/>
       <c r="C99" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B18</f>
         <v>SZ0002</v>
@@ -8536,8 +8536,8 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A100" s="105"/>
-      <c r="B100" s="105"/>
+      <c r="A100" s="115"/>
+      <c r="B100" s="115"/>
       <c r="C100" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B19</f>
         <v>SZ0003</v>
@@ -8564,8 +8564,8 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A101" s="105"/>
-      <c r="B101" s="105"/>
+      <c r="A101" s="115"/>
+      <c r="B101" s="115"/>
       <c r="C101" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B20</f>
         <v>SB0022</v>
@@ -8592,8 +8592,8 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A102" s="105"/>
-      <c r="B102" s="105"/>
+      <c r="A102" s="115"/>
+      <c r="B102" s="115"/>
       <c r="C102" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B21</f>
         <v>SB0006</v>
@@ -8620,8 +8620,8 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A103" s="105"/>
-      <c r="B103" s="105"/>
+      <c r="A103" s="115"/>
+      <c r="B103" s="115"/>
       <c r="C103" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B22</f>
         <v>SZ0005</v>
@@ -8648,8 +8648,8 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A104" s="105"/>
-      <c r="B104" s="105"/>
+      <c r="A104" s="115"/>
+      <c r="B104" s="115"/>
       <c r="C104" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B23</f>
         <v>SC0004</v>
@@ -8676,8 +8676,8 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A105" s="105"/>
-      <c r="B105" s="105"/>
+      <c r="A105" s="115"/>
+      <c r="B105" s="115"/>
       <c r="C105" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B24</f>
         <v>SC0010</v>
@@ -8704,8 +8704,8 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A106" s="105"/>
-      <c r="B106" s="105"/>
+      <c r="A106" s="115"/>
+      <c r="B106" s="115"/>
       <c r="C106" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B25</f>
         <v>SC0002</v>
@@ -8732,8 +8732,8 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A107" s="105"/>
-      <c r="B107" s="105"/>
+      <c r="A107" s="115"/>
+      <c r="B107" s="115"/>
       <c r="C107" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B26</f>
         <v>SC0003</v>
@@ -8760,8 +8760,8 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A108" s="105"/>
-      <c r="B108" s="105"/>
+      <c r="A108" s="115"/>
+      <c r="B108" s="115"/>
       <c r="C108" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B27</f>
         <v>SC0005</v>
@@ -8788,8 +8788,8 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A109" s="105"/>
-      <c r="B109" s="105"/>
+      <c r="A109" s="115"/>
+      <c r="B109" s="115"/>
       <c r="C109" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B28</f>
         <v>SS0003</v>
@@ -8816,8 +8816,8 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110" s="105"/>
-      <c r="B110" s="105"/>
+      <c r="A110" s="115"/>
+      <c r="B110" s="115"/>
       <c r="C110" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B29</f>
         <v>SZ0012</v>
@@ -8844,8 +8844,8 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A111" s="105"/>
-      <c r="B111" s="105"/>
+      <c r="A111" s="115"/>
+      <c r="B111" s="115"/>
       <c r="C111" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B30</f>
         <v>SZ0014</v>
@@ -8872,8 +8872,8 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A112" s="105"/>
-      <c r="B112" s="105"/>
+      <c r="A112" s="115"/>
+      <c r="B112" s="115"/>
       <c r="C112" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B31</f>
         <v>SE0003</v>
@@ -8900,8 +8900,8 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A113" s="105"/>
-      <c r="B113" s="105"/>
+      <c r="A113" s="115"/>
+      <c r="B113" s="115"/>
       <c r="C113" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B32</f>
         <v>SZ0019</v>
@@ -8928,8 +8928,8 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A114" s="105"/>
-      <c r="B114" s="105"/>
+      <c r="A114" s="115"/>
+      <c r="B114" s="115"/>
       <c r="C114" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B33</f>
         <v>SZ0020</v>
@@ -8956,8 +8956,8 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A115" s="105"/>
-      <c r="B115" s="105"/>
+      <c r="A115" s="115"/>
+      <c r="B115" s="115"/>
       <c r="C115" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B34</f>
         <v>SB0011</v>
@@ -8984,8 +8984,8 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A116" s="105"/>
-      <c r="B116" s="105"/>
+      <c r="A116" s="115"/>
+      <c r="B116" s="115"/>
       <c r="C116" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B35</f>
         <v>SZ0004</v>
@@ -9012,8 +9012,8 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A117" s="105"/>
-      <c r="B117" s="105"/>
+      <c r="A117" s="115"/>
+      <c r="B117" s="115"/>
       <c r="C117" s="14" t="str">
         <f>'BOM_(개조) HiNAS Con SVM'!B36</f>
         <v>SM0005</v>
@@ -9040,10 +9040,10 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A118" s="106" t="s">
+      <c r="A118" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="B118" s="106" t="s">
+      <c r="B118" s="116" t="s">
         <v>35</v>
       </c>
       <c r="C118" s="15" t="str">
@@ -9072,8 +9072,8 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A119" s="106"/>
-      <c r="B119" s="106"/>
+      <c r="A119" s="116"/>
+      <c r="B119" s="116"/>
       <c r="C119" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B12</f>
         <v>SS0001</v>
@@ -9100,8 +9100,8 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A120" s="106"/>
-      <c r="B120" s="106"/>
+      <c r="A120" s="116"/>
+      <c r="B120" s="116"/>
       <c r="C120" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B13</f>
         <v>SS0003</v>
@@ -9128,8 +9128,8 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A121" s="106"/>
-      <c r="B121" s="106"/>
+      <c r="A121" s="116"/>
+      <c r="B121" s="116"/>
       <c r="C121" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B14</f>
         <v>SC0010</v>
@@ -9156,8 +9156,8 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A122" s="106"/>
-      <c r="B122" s="106"/>
+      <c r="A122" s="116"/>
+      <c r="B122" s="116"/>
       <c r="C122" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B15</f>
         <v>SC0002</v>
@@ -9184,8 +9184,8 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A123" s="106"/>
-      <c r="B123" s="106"/>
+      <c r="A123" s="116"/>
+      <c r="B123" s="116"/>
       <c r="C123" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B16</f>
         <v>SC0003</v>
@@ -9212,8 +9212,8 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A124" s="106"/>
-      <c r="B124" s="106"/>
+      <c r="A124" s="116"/>
+      <c r="B124" s="116"/>
       <c r="C124" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B17</f>
         <v>SC0004</v>
@@ -9240,8 +9240,8 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A125" s="106"/>
-      <c r="B125" s="106"/>
+      <c r="A125" s="116"/>
+      <c r="B125" s="116"/>
       <c r="C125" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B18</f>
         <v>SC0005</v>
@@ -9268,8 +9268,8 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A126" s="106"/>
-      <c r="B126" s="106"/>
+      <c r="A126" s="116"/>
+      <c r="B126" s="116"/>
       <c r="C126" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B19</f>
         <v>SB0002</v>
@@ -9296,8 +9296,8 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A127" s="106"/>
-      <c r="B127" s="106"/>
+      <c r="A127" s="116"/>
+      <c r="B127" s="116"/>
       <c r="C127" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B20</f>
         <v>SB0004</v>
@@ -9324,8 +9324,8 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A128" s="106"/>
-      <c r="B128" s="106"/>
+      <c r="A128" s="116"/>
+      <c r="B128" s="116"/>
       <c r="C128" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B21</f>
         <v>SB0006</v>
@@ -9352,8 +9352,8 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A129" s="106"/>
-      <c r="B129" s="106"/>
+      <c r="A129" s="116"/>
+      <c r="B129" s="116"/>
       <c r="C129" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B22</f>
         <v>SB0011</v>
@@ -9380,8 +9380,8 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A130" s="106"/>
-      <c r="B130" s="106"/>
+      <c r="A130" s="116"/>
+      <c r="B130" s="116"/>
       <c r="C130" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B23</f>
         <v>SE0003</v>
@@ -9408,8 +9408,8 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="106"/>
-      <c r="B131" s="106"/>
+      <c r="A131" s="116"/>
+      <c r="B131" s="116"/>
       <c r="C131" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B24</f>
         <v>SZ0005</v>
@@ -9436,8 +9436,8 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A132" s="106"/>
-      <c r="B132" s="106"/>
+      <c r="A132" s="116"/>
+      <c r="B132" s="116"/>
       <c r="C132" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B25</f>
         <v>SZ0004</v>
@@ -9464,8 +9464,8 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A133" s="106"/>
-      <c r="B133" s="106"/>
+      <c r="A133" s="116"/>
+      <c r="B133" s="116"/>
       <c r="C133" s="15" t="str">
         <f>'BOM_(개조) HiNAS Control'!B26</f>
         <v>SM0005</v>
@@ -9493,12 +9493,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="B2:B16"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="A17:A32"/>
-    <mergeCell ref="B17:B32"/>
-    <mergeCell ref="K3:K13"/>
     <mergeCell ref="A92:A117"/>
     <mergeCell ref="B92:B117"/>
     <mergeCell ref="A118:A133"/>
@@ -9509,6 +9503,12 @@
     <mergeCell ref="B55:B75"/>
     <mergeCell ref="A76:A91"/>
     <mergeCell ref="B76:B91"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B16"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="A17:A32"/>
+    <mergeCell ref="B17:B32"/>
+    <mergeCell ref="K3:K13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9824,23 +9824,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.45">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C3" s="16" t="s">
@@ -9956,10 +9956,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -10836,38 +10836,38 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C27" s="116" t="s">
+      <c r="C27" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="116"/>
-      <c r="N27" s="116"/>
-      <c r="O27" s="116"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="120"/>
     </row>
     <row r="28" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C28" s="116" t="s">
+      <c r="C28" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="116"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10910,23 +10910,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.45">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C3" s="16" t="s">
@@ -11042,10 +11042,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -11978,38 +11978,38 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C28" s="116" t="s">
+      <c r="C28" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="116"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
     </row>
     <row r="29" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C29" s="116" t="s">
+      <c r="C29" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
+      <c r="O29" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12051,23 +12051,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" ht="30" x14ac:dyDescent="0.45">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="C3" s="16" t="s">
@@ -12180,10 +12180,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -13505,38 +13505,38 @@
       <c r="O33" s="31"/>
     </row>
     <row r="34" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C34" s="116" t="s">
+      <c r="C34" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="116"/>
-      <c r="M34" s="116"/>
-      <c r="N34" s="116"/>
-      <c r="O34" s="116"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="120"/>
+      <c r="M34" s="120"/>
+      <c r="N34" s="120"/>
+      <c r="O34" s="120"/>
     </row>
     <row r="35" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C35" s="116" t="s">
+      <c r="C35" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="116"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="116"/>
-      <c r="L35" s="116"/>
-      <c r="M35" s="116"/>
-      <c r="N35" s="116"/>
-      <c r="O35" s="116"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="120"/>
+      <c r="I35" s="120"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="120"/>
+      <c r="O35" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13578,23 +13578,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.45">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C3" s="16" t="s">
@@ -13707,10 +13707,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -14924,38 +14924,38 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C32" s="116" t="s">
+      <c r="C32" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="116"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="116"/>
-      <c r="H32" s="116"/>
-      <c r="I32" s="116"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="116"/>
-      <c r="M32" s="116"/>
-      <c r="N32" s="116"/>
-      <c r="O32" s="116"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="120"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="120"/>
+      <c r="M32" s="120"/>
+      <c r="N32" s="120"/>
+      <c r="O32" s="120"/>
     </row>
     <row r="33" spans="3:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C33" s="116" t="s">
+      <c r="C33" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="116"/>
-      <c r="H33" s="116"/>
-      <c r="I33" s="116"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="116"/>
-      <c r="L33" s="116"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="116"/>
-      <c r="O33" s="116"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="120"/>
+      <c r="L33" s="120"/>
+      <c r="M33" s="120"/>
+      <c r="N33" s="120"/>
+      <c r="O33" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15014,23 +15014,23 @@
       <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.75">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="34"/>
@@ -15176,10 +15176,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -16132,40 +16132,40 @@
     <row r="28" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A28" s="34"/>
       <c r="B28" s="34"/>
-      <c r="C28" s="118" t="s">
+      <c r="C28" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="118"/>
-      <c r="N28" s="118"/>
-      <c r="O28" s="118"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="122"/>
+      <c r="I28" s="122"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="122"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="122"/>
     </row>
     <row r="29" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A29" s="34"/>
       <c r="B29" s="34"/>
-      <c r="C29" s="118" t="s">
+      <c r="C29" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="118"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="122"/>
+      <c r="I29" s="122"/>
+      <c r="J29" s="122"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="122"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="122"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" s="34"/>
@@ -16241,23 +16241,23 @@
       <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.75">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="34"/>
@@ -16403,10 +16403,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -17958,40 +17958,40 @@
     <row r="38" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A38" s="34"/>
       <c r="B38" s="34"/>
-      <c r="C38" s="118" t="s">
+      <c r="C38" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-      <c r="K38" s="118"/>
-      <c r="L38" s="118"/>
-      <c r="M38" s="118"/>
-      <c r="N38" s="118"/>
-      <c r="O38" s="118"/>
+      <c r="D38" s="122"/>
+      <c r="E38" s="122"/>
+      <c r="F38" s="122"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="122"/>
+      <c r="I38" s="122"/>
+      <c r="J38" s="122"/>
+      <c r="K38" s="122"/>
+      <c r="L38" s="122"/>
+      <c r="M38" s="122"/>
+      <c r="N38" s="122"/>
+      <c r="O38" s="122"/>
     </row>
     <row r="39" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A39" s="34"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="118" t="s">
+      <c r="C39" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="D39" s="118"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="118"/>
-      <c r="G39" s="118"/>
-      <c r="H39" s="118"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="118"/>
-      <c r="K39" s="118"/>
-      <c r="L39" s="118"/>
-      <c r="M39" s="118"/>
-      <c r="N39" s="118"/>
-      <c r="O39" s="118"/>
+      <c r="D39" s="122"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="122"/>
+      <c r="N39" s="122"/>
+      <c r="O39" s="122"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40" s="34"/>
@@ -18050,23 +18050,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.45">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="C3" s="16" t="s">
@@ -18182,10 +18182,10 @@
       <c r="B10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="115"/>
+      <c r="D10" s="119"/>
       <c r="E10" s="24" t="s">
         <v>50</v>
       </c>
@@ -19136,38 +19136,38 @@
       <c r="O27" s="31"/>
     </row>
     <row r="28" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C28" s="116" t="s">
+      <c r="C28" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="116"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
     </row>
     <row r="29" spans="1:15" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C29" s="116" t="s">
+      <c r="C29" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
+      <c r="O29" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -19320,16 +19320,16 @@
       <c r="R4" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="S4" s="119" t="s">
+      <c r="S4" s="123" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120"/>
-      <c r="V4" s="121"/>
-      <c r="X4" s="122" t="s">
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="125"/>
+      <c r="X4" s="126" t="s">
         <v>141</v>
       </c>
-      <c r="Y4" s="123"/>
+      <c r="Y4" s="127"/>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" s="54" t="s">
@@ -23265,15 +23265,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="24019410-d1d0-42fe-b6da-bfb21a3ee566">
@@ -23285,6 +23276,15 @@
     <TaxCatchAll xmlns="f1fa6c51-b02d-4139-aafb-3ade645604da" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23307,14 +23307,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BACD74DF-83B6-4A47-80C9-DEDD06725520}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D135BCFC-3384-4D23-8DF3-4B60E8B2F734}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -23325,6 +23317,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BACD74DF-83B6-4A47-80C9-DEDD06725520}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{48141450-2387-4aca-b41f-19cd6be9dd3c}" enabled="1" method="Standard" siteId="{adf10e2b-b6e9-41d6-be2f-c12bb566019c}" removed="0"/>
